--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127840593</v>
       </c>
       <c r="B2" t="n">
-        <v>58093</v>
+        <v>58096</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>127840817</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>127840503</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>127840755</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>127840604</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127840997</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>127841273</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>127840656</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127840593</v>
       </c>
       <c r="B2" t="n">
-        <v>58096</v>
+        <v>58102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>127840817</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>127840503</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>127840755</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>127840604</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127840997</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>127841273</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>127840656</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127840593</v>
       </c>
       <c r="B2" t="n">
-        <v>58102</v>
+        <v>58103</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>127840817</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>127840503</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>127840755</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>127840604</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127840997</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>127841273</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>127840656</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127840593</v>
       </c>
       <c r="B2" t="n">
-        <v>58103</v>
+        <v>58115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>127840817</v>
       </c>
       <c r="B3" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>127840503</v>
       </c>
       <c r="B4" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>127840755</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>127840604</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127840997</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>127841273</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>127840656</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>127840503</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>127840755</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>127840604</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127840997</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>127841273</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>127840656</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1569,6 +1569,3993 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129149060</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>491763</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6764994</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 40 meter 2 bilder</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129149167</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>491747</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6765080</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Bild</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129147059</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>491660</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6765053</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129147386</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>491600</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6765059</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129145482</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>491605</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6765075</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129147406</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>491605</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6765052</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129147986</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>491639</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6764969</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129147300</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>491625</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6765040</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Garn samt 3 miljöbilder</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129146972</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>491643</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6765056</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129147806</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>491641</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6765032</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129147916</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97522</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>491639</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6764969</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Revlummer samt 2 miljöbilder</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129148872</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>491782</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6765017</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Bild</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129146351</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>491626</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6765093</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129146949</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>491660</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6765085</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129147148</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>491656</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6765038</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129149409</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>491784</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6765153</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129148629</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>491834</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6765056</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129147447</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>491606</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6765045</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129148685</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>491835</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6765066</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt i gran samt tallar 2 bilder</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129148571</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>491827</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6765046</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129148408</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>491876</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6764940</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter Ca tio bilder tagna</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129147170</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>491656</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6765038</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Bild 3 spillkr</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129148866</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>491782</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6765017</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 30 meter</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129148294</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>491862</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6764868</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129145950</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>491626</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6765093</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129146456</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>491626</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6765093</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129146529</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>491659</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6765108</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129147379</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>491602</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6765069</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129148942</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>491791</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6765007</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2 bilder</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129146427</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>491626</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6765093</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129145705</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>491605</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6765075</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129146961</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57883</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>491652</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6765086</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129148524</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>491825</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6765020</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>I gran</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129148485</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>491823</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6764963</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129148592</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>491827</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6765046</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129149092</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>491755</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6765029</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1571,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129149060</v>
+        <v>129147059</v>
       </c>
       <c r="B10" t="n">
         <v>79034</v>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491763</v>
+        <v>491660</v>
       </c>
       <c r="R10" t="n">
-        <v>6764994</v>
+        <v>6765053</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,12 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 40 meter 2 bilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129149167</v>
+        <v>129147386</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,39 +1689,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491747</v>
+        <v>491600</v>
       </c>
       <c r="R11" t="n">
-        <v>6765080</v>
+        <v>6765059</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,12 +1758,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Bild</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129147059</v>
+        <v>129147406</v>
       </c>
       <c r="B12" t="n">
         <v>79034</v>
@@ -1835,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491660</v>
+        <v>491605</v>
       </c>
       <c r="R12" t="n">
-        <v>6765053</v>
+        <v>6765052</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1892,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129147386</v>
+        <v>129145482</v>
       </c>
       <c r="B13" t="n">
         <v>79034</v>
@@ -1942,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491600</v>
+        <v>491605</v>
       </c>
       <c r="R13" t="n">
-        <v>6765059</v>
+        <v>6765075</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +1999,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129145482</v>
+        <v>129147986</v>
       </c>
       <c r="B14" t="n">
         <v>79034</v>
@@ -2049,10 +2034,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491605</v>
+        <v>491639</v>
       </c>
       <c r="R14" t="n">
-        <v>6765075</v>
+        <v>6764969</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2106,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129147406</v>
+        <v>129146972</v>
       </c>
       <c r="B15" t="n">
         <v>79034</v>
@@ -2156,10 +2141,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491605</v>
+        <v>491643</v>
       </c>
       <c r="R15" t="n">
-        <v>6765052</v>
+        <v>6765056</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,7 +2213,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129147986</v>
+        <v>129147806</v>
       </c>
       <c r="B16" t="n">
         <v>79034</v>
@@ -2263,10 +2248,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491639</v>
+        <v>491641</v>
       </c>
       <c r="R16" t="n">
-        <v>6764969</v>
+        <v>6765032</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2335,7 +2320,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129147300</v>
+        <v>129147148</v>
       </c>
       <c r="B17" t="n">
         <v>79034</v>
@@ -2370,10 +2355,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491625</v>
+        <v>491656</v>
       </c>
       <c r="R17" t="n">
-        <v>6765040</v>
+        <v>6765038</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2416,11 +2401,6 @@
       <c r="AB17" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Garn samt 3 miljöbilder</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2447,7 +2427,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129146972</v>
+        <v>129146949</v>
       </c>
       <c r="B18" t="n">
         <v>79034</v>
@@ -2482,10 +2462,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491643</v>
+        <v>491660</v>
       </c>
       <c r="R18" t="n">
-        <v>6765056</v>
+        <v>6765085</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2554,7 +2534,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129147806</v>
+        <v>129148629</v>
       </c>
       <c r="B19" t="n">
         <v>79034</v>
@@ -2589,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491641</v>
+        <v>491834</v>
       </c>
       <c r="R19" t="n">
-        <v>6765032</v>
+        <v>6765056</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2635,6 +2615,11 @@
       <c r="AB19" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2661,32 +2646,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129147916</v>
+        <v>129147447</v>
       </c>
       <c r="B20" t="n">
-        <v>97522</v>
+        <v>79034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2696,10 +2681,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491639</v>
+        <v>491606</v>
       </c>
       <c r="R20" t="n">
-        <v>6764969</v>
+        <v>6765045</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2742,11 +2727,6 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Revlummer samt 2 miljöbilder</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,10 +2753,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129148872</v>
+        <v>129145950</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2784,39 +2764,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491782</v>
+        <v>491626</v>
       </c>
       <c r="R21" t="n">
-        <v>6765017</v>
+        <v>6765093</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2848,7 +2823,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2858,12 +2833,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Bild</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2890,40 +2860,35 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129146351</v>
+        <v>129146456</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
@@ -3002,7 +2967,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129146949</v>
+        <v>129147379</v>
       </c>
       <c r="B23" t="n">
         <v>79034</v>
@@ -3037,10 +3002,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491660</v>
+        <v>491602</v>
       </c>
       <c r="R23" t="n">
-        <v>6765085</v>
+        <v>6765069</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3109,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129147148</v>
+        <v>129146427</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3120,34 +3085,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491656</v>
+        <v>491626</v>
       </c>
       <c r="R24" t="n">
-        <v>6765038</v>
+        <v>6765093</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3216,10 +3186,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129149409</v>
+        <v>129146961</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>57883</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3227,34 +3197,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491784</v>
+        <v>491652</v>
       </c>
       <c r="R25" t="n">
-        <v>6765153</v>
+        <v>6765086</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3286,7 +3261,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3296,12 +3271,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3328,10 +3298,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129148629</v>
+        <v>129148592</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3339,34 +3309,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491834</v>
+        <v>491827</v>
       </c>
       <c r="R26" t="n">
-        <v>6765056</v>
+        <v>6765046</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3409,11 +3384,6 @@
       <c r="AB26" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3440,7 +3410,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129147447</v>
+        <v>129149092</v>
       </c>
       <c r="B27" t="n">
         <v>79034</v>
@@ -3475,10 +3445,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491606</v>
+        <v>491755</v>
       </c>
       <c r="R27" t="n">
-        <v>6765045</v>
+        <v>6765029</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3510,7 +3480,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3520,7 +3490,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3547,7 +3522,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129148685</v>
+        <v>129149060</v>
       </c>
       <c r="B28" t="n">
         <v>79034</v>
@@ -3576,16 +3551,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491835</v>
+        <v>491763</v>
       </c>
       <c r="R28" t="n">
-        <v>6765066</v>
+        <v>6764994</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3617,7 +3595,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3627,12 +3605,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt i gran samt tallar 2 bilder</t>
+          <t>Rikligt i en radie av 40 meter 1 bild</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3641,6 +3619,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3659,10 +3638,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129148571</v>
+        <v>129149167</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3670,34 +3649,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491827</v>
+        <v>491747</v>
       </c>
       <c r="R29" t="n">
-        <v>6765046</v>
+        <v>6765080</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3729,7 +3716,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3739,12 +3726,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3771,7 +3753,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129148408</v>
+        <v>129147300</v>
       </c>
       <c r="B30" t="n">
         <v>79034</v>
@@ -3806,10 +3788,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491876</v>
+        <v>491625</v>
       </c>
       <c r="R30" t="n">
-        <v>6764940</v>
+        <v>6765040</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3856,7 +3838,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter Ca tio bilder tagna</t>
+          <t>Garn samt 3 miljöbilder</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3883,50 +3865,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129147170</v>
+        <v>129147916</v>
       </c>
       <c r="B31" t="n">
-        <v>57720</v>
+        <v>97527</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491656</v>
+        <v>491639</v>
       </c>
       <c r="R31" t="n">
-        <v>6765038</v>
+        <v>6764969</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3973,7 +3950,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Bild 3 spillkr</t>
+          <t>Revlummer samt 2 miljöbilder</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4000,10 +3977,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129148866</v>
+        <v>129148872</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4011,24 +3988,29 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
@@ -4085,7 +4067,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 30 meter</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4112,10 +4094,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129148294</v>
+        <v>129146351</v>
       </c>
       <c r="B33" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4123,34 +4105,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491862</v>
+        <v>491626</v>
       </c>
       <c r="R33" t="n">
-        <v>6764868</v>
+        <v>6765093</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4193,11 +4180,6 @@
       <c r="AB33" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4224,7 +4206,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129145950</v>
+        <v>129149409</v>
       </c>
       <c r="B34" t="n">
         <v>79034</v>
@@ -4253,16 +4235,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491626</v>
+        <v>491784</v>
       </c>
       <c r="R34" t="n">
-        <v>6765093</v>
+        <v>6765153</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4294,7 +4279,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4304,7 +4289,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter samt miljöbilder</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4313,6 +4303,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4331,32 +4322,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129146456</v>
+        <v>129148685</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4366,10 +4357,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491626</v>
+        <v>491835</v>
       </c>
       <c r="R35" t="n">
-        <v>6765093</v>
+        <v>6765066</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4412,6 +4403,11 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt i gran samt tallar 2 bilder</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4438,10 +4434,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129146529</v>
+        <v>129148571</v>
       </c>
       <c r="B36" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4449,39 +4445,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491659</v>
+        <v>491827</v>
       </c>
       <c r="R36" t="n">
-        <v>6765108</v>
+        <v>6765046</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4524,6 +4515,11 @@
       <c r="AB36" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4550,7 +4546,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129147379</v>
+        <v>129148408</v>
       </c>
       <c r="B37" t="n">
         <v>79034</v>
@@ -4585,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491602</v>
+        <v>491876</v>
       </c>
       <c r="R37" t="n">
-        <v>6765069</v>
+        <v>6764940</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4631,6 +4627,11 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter Ca tio bilder tagna</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4657,10 +4658,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129148942</v>
+        <v>129147170</v>
       </c>
       <c r="B38" t="n">
-        <v>57723</v>
+        <v>57720</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4668,16 +4669,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4688,7 +4689,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4697,10 +4698,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491791</v>
+        <v>491656</v>
       </c>
       <c r="R38" t="n">
-        <v>6765007</v>
+        <v>6765038</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4732,7 +4733,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4742,12 +4743,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>2 bilder</t>
+          <t>Bild 3 spillkr</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4774,10 +4775,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129146427</v>
+        <v>129148866</v>
       </c>
       <c r="B39" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4785,39 +4786,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491626</v>
+        <v>491782</v>
       </c>
       <c r="R39" t="n">
-        <v>6765093</v>
+        <v>6765017</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4849,7 +4845,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4859,7 +4855,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 30 meter</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4886,10 +4887,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129145705</v>
+        <v>129148294</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4897,39 +4898,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491605</v>
+        <v>491862</v>
       </c>
       <c r="R40" t="n">
-        <v>6765075</v>
+        <v>6764868</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4972,6 +4968,11 @@
       <c r="AB40" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4998,10 +4999,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129146961</v>
+        <v>129146529</v>
       </c>
       <c r="B41" t="n">
-        <v>57883</v>
+        <v>57720</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5009,27 +5010,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5038,10 +5039,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491652</v>
+        <v>491659</v>
       </c>
       <c r="R41" t="n">
-        <v>6765086</v>
+        <v>6765108</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5110,10 +5111,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129148524</v>
+        <v>129148972</v>
       </c>
       <c r="B42" t="n">
-        <v>79034</v>
+        <v>91523</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5121,34 +5122,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491825</v>
+        <v>491791</v>
       </c>
       <c r="R42" t="n">
-        <v>6765020</v>
+        <v>6765007</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5180,7 +5184,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5190,12 +5194,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>I gran</t>
+          <t>Vedsvamp, granlåga, 3 bilder</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5204,6 +5208,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5222,10 +5227,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129148485</v>
+        <v>129148942</v>
       </c>
       <c r="B43" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5233,34 +5238,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491823</v>
+        <v>491791</v>
       </c>
       <c r="R43" t="n">
-        <v>6764963</v>
+        <v>6765007</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5292,7 +5302,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5302,12 +5312,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5334,10 +5344,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129148592</v>
+        <v>129148524</v>
       </c>
       <c r="B44" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5345,39 +5355,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491827</v>
+        <v>491825</v>
       </c>
       <c r="R44" t="n">
-        <v>6765046</v>
+        <v>6765020</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5420,6 +5425,11 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>I gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5446,10 +5456,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129149092</v>
+        <v>129145705</v>
       </c>
       <c r="B45" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5457,34 +5467,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491755</v>
+        <v>491605</v>
       </c>
       <c r="R45" t="n">
-        <v>6765029</v>
+        <v>6765075</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5516,7 +5531,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5526,12 +5541,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5555,6 +5565,118 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129148485</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Toktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>491823</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6764963</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>129147059</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>129147386</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>129147406</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>129145482</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>129147986</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>129146972</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>129147806</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>129147148</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>129146949</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129148629</v>
+        <v>129147447</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491834</v>
+        <v>491606</v>
       </c>
       <c r="R19" t="n">
-        <v>6765056</v>
+        <v>6765045</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,11 +2615,6 @@
       <c r="AB19" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2646,10 +2641,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129147447</v>
+        <v>129148629</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491606</v>
+        <v>491834</v>
       </c>
       <c r="R20" t="n">
-        <v>6765045</v>
+        <v>6765056</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2727,6 +2722,11 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2753,32 +2753,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129145950</v>
+        <v>129146456</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2860,32 +2860,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129146456</v>
+        <v>129145950</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2970,7 +2970,7 @@
         <v>129147379</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129146427</v>
+        <v>129146961</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>57883</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3085,27 +3085,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491626</v>
+        <v>491652</v>
       </c>
       <c r="R24" t="n">
-        <v>6765093</v>
+        <v>6765086</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,10 +3186,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129146961</v>
+        <v>129146427</v>
       </c>
       <c r="B25" t="n">
-        <v>57883</v>
+        <v>57720</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3197,27 +3197,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491652</v>
+        <v>491626</v>
       </c>
       <c r="R25" t="n">
-        <v>6765086</v>
+        <v>6765093</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3413,7 +3413,7 @@
         <v>129149092</v>
       </c>
       <c r="B27" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>129149060</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>129147300</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129147916</v>
       </c>
       <c r="B31" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4094,10 +4094,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129146351</v>
+        <v>129149409</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4105,39 +4105,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491626</v>
+        <v>491784</v>
       </c>
       <c r="R33" t="n">
-        <v>6765093</v>
+        <v>6765153</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4169,7 +4167,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4179,7 +4177,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter samt miljöbilder</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4188,6 +4191,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4206,10 +4210,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129149409</v>
+        <v>129146351</v>
       </c>
       <c r="B34" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4217,37 +4221,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491784</v>
+        <v>491626</v>
       </c>
       <c r="R34" t="n">
-        <v>6765153</v>
+        <v>6765093</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4279,7 +4285,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4289,12 +4295,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter samt miljöbilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4303,7 +4304,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>129148685</v>
       </c>
       <c r="B35" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>129148571</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>129148408</v>
       </c>
       <c r="B37" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129147170</v>
+        <v>129148866</v>
       </c>
       <c r="B38" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,39 +4669,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491656</v>
+        <v>491782</v>
       </c>
       <c r="R38" t="n">
-        <v>6765038</v>
+        <v>6765017</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4733,7 +4728,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4743,12 +4738,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Bild 3 spillkr</t>
+          <t>Rikligt i en radie av 30 meter</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4775,10 +4770,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129148866</v>
+        <v>129147170</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4786,34 +4781,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491782</v>
+        <v>491656</v>
       </c>
       <c r="R39" t="n">
-        <v>6765017</v>
+        <v>6765038</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 30 meter</t>
+          <t>Bild 3 spillkr</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4890,7 +4890,7 @@
         <v>129148294</v>
       </c>
       <c r="B40" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>129148972</v>
       </c>
       <c r="B42" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5344,10 +5344,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129148524</v>
+        <v>129145705</v>
       </c>
       <c r="B44" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5355,34 +5355,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491825</v>
+        <v>491605</v>
       </c>
       <c r="R44" t="n">
-        <v>6765020</v>
+        <v>6765075</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5425,11 +5430,6 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>I gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,10 +5456,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129145705</v>
+        <v>129148524</v>
       </c>
       <c r="B45" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5467,39 +5467,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491605</v>
+        <v>491825</v>
       </c>
       <c r="R45" t="n">
-        <v>6765075</v>
+        <v>6765020</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5542,6 +5537,11 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>I gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5571,7 +5571,7 @@
         <v>129148485</v>
       </c>
       <c r="B46" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -2753,32 +2753,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129146456</v>
+        <v>129145950</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2860,32 +2860,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129145950</v>
+        <v>129146456</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129146529</v>
+        <v>129148972</v>
       </c>
       <c r="B41" t="n">
-        <v>57720</v>
+        <v>91526</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5010,39 +5010,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491659</v>
+        <v>491791</v>
       </c>
       <c r="R41" t="n">
-        <v>6765108</v>
+        <v>6765007</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5074,7 +5072,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5084,7 +5082,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Vedsvamp, granlåga, 3 bilder</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5093,6 +5096,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5111,10 +5115,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129148972</v>
+        <v>129146529</v>
       </c>
       <c r="B42" t="n">
-        <v>91526</v>
+        <v>57720</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5122,37 +5126,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491791</v>
+        <v>491659</v>
       </c>
       <c r="R42" t="n">
-        <v>6765007</v>
+        <v>6765108</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5184,7 +5190,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5194,12 +5200,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Vedsvamp, granlåga, 3 bilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5208,7 +5209,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5344,10 +5344,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129145705</v>
+        <v>129148524</v>
       </c>
       <c r="B44" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5355,39 +5355,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491605</v>
+        <v>491825</v>
       </c>
       <c r="R44" t="n">
-        <v>6765075</v>
+        <v>6765020</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5430,6 +5425,11 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>I gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,7 +5456,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129148524</v>
+        <v>129148485</v>
       </c>
       <c r="B45" t="n">
         <v>79035</v>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491825</v>
+        <v>491823</v>
       </c>
       <c r="R45" t="n">
-        <v>6765020</v>
+        <v>6764963</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>I gran</t>
+          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5568,10 +5568,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129148485</v>
+        <v>129145705</v>
       </c>
       <c r="B46" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5579,34 +5579,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491823</v>
+        <v>491605</v>
       </c>
       <c r="R46" t="n">
-        <v>6764963</v>
+        <v>6765075</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5649,11 +5654,6 @@
       <c r="AB46" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129147059</v>
+        <v>129147386</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491660</v>
+        <v>491600</v>
       </c>
       <c r="R10" t="n">
-        <v>6765053</v>
+        <v>6765059</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129147386</v>
+        <v>129147059</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491600</v>
+        <v>491660</v>
       </c>
       <c r="R11" t="n">
-        <v>6765059</v>
+        <v>6765053</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
         <v>129147406</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>129145482</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>129147986</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>129146972</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>129147806</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>129147148</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>129146949</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129147447</v>
+        <v>129148629</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491606</v>
+        <v>491834</v>
       </c>
       <c r="R19" t="n">
-        <v>6765045</v>
+        <v>6765056</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,6 +2615,11 @@
       <c r="AB19" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2641,10 +2646,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129148629</v>
+        <v>129147447</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2676,10 +2681,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491834</v>
+        <v>491606</v>
       </c>
       <c r="R20" t="n">
-        <v>6765056</v>
+        <v>6765045</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2722,11 +2727,6 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2756,7 +2756,7 @@
         <v>129145950</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>129147379</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129146961</v>
+        <v>129146427</v>
       </c>
       <c r="B24" t="n">
-        <v>57883</v>
+        <v>57722</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3085,27 +3085,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491652</v>
+        <v>491626</v>
       </c>
       <c r="R24" t="n">
-        <v>6765086</v>
+        <v>6765093</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,10 +3186,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129146427</v>
+        <v>129146961</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>57885</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3197,27 +3197,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491626</v>
+        <v>491652</v>
       </c>
       <c r="R25" t="n">
-        <v>6765093</v>
+        <v>6765086</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3301,7 +3301,7 @@
         <v>129148592</v>
       </c>
       <c r="B26" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>129149092</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>129149060</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>129149167</v>
       </c>
       <c r="B29" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>129147300</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129147916</v>
       </c>
       <c r="B31" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>129148872</v>
       </c>
       <c r="B32" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>129149409</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>129146351</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>129148685</v>
       </c>
       <c r="B35" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>129148571</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>129148408</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>129148866</v>
       </c>
       <c r="B38" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>129147170</v>
       </c>
       <c r="B39" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>129148294</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>129148972</v>
       </c>
       <c r="B41" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>129146529</v>
       </c>
       <c r="B42" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>129148942</v>
       </c>
       <c r="B43" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5344,10 +5344,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129148524</v>
+        <v>129148485</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491825</v>
+        <v>491823</v>
       </c>
       <c r="R44" t="n">
-        <v>6765020</v>
+        <v>6764963</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>I gran</t>
+          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,10 +5456,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129148485</v>
+        <v>129148524</v>
       </c>
       <c r="B45" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491823</v>
+        <v>491825</v>
       </c>
       <c r="R45" t="n">
-        <v>6764963</v>
+        <v>6765020</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
+          <t>I gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5571,7 +5571,7 @@
         <v>129145705</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129146427</v>
+        <v>129146961</v>
       </c>
       <c r="B24" t="n">
-        <v>57722</v>
+        <v>57885</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3085,27 +3085,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491626</v>
+        <v>491652</v>
       </c>
       <c r="R24" t="n">
-        <v>6765093</v>
+        <v>6765086</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,10 +3186,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129146961</v>
+        <v>129146427</v>
       </c>
       <c r="B25" t="n">
-        <v>57885</v>
+        <v>57722</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3197,27 +3197,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491652</v>
+        <v>491626</v>
       </c>
       <c r="R25" t="n">
-        <v>6765086</v>
+        <v>6765093</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129148866</v>
+        <v>129147170</v>
       </c>
       <c r="B38" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,34 +4669,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491782</v>
+        <v>491656</v>
       </c>
       <c r="R38" t="n">
-        <v>6765017</v>
+        <v>6765038</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4728,7 +4733,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4738,12 +4743,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 30 meter</t>
+          <t>Bild 3 spillkr</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4770,10 +4775,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129147170</v>
+        <v>129148866</v>
       </c>
       <c r="B39" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4781,39 +4786,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491656</v>
+        <v>491782</v>
       </c>
       <c r="R39" t="n">
-        <v>6765038</v>
+        <v>6765017</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Bild 3 spillkr</t>
+          <t>Rikligt i en radie av 30 meter</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -1571,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129147386</v>
+        <v>129147059</v>
       </c>
       <c r="B10" t="n">
         <v>79039</v>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491600</v>
+        <v>491660</v>
       </c>
       <c r="R10" t="n">
-        <v>6765059</v>
+        <v>6765053</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129147059</v>
+        <v>129147386</v>
       </c>
       <c r="B11" t="n">
         <v>79039</v>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491660</v>
+        <v>491600</v>
       </c>
       <c r="R11" t="n">
-        <v>6765053</v>
+        <v>6765059</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2534,7 +2534,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129148629</v>
+        <v>129147447</v>
       </c>
       <c r="B19" t="n">
         <v>79039</v>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491834</v>
+        <v>491606</v>
       </c>
       <c r="R19" t="n">
-        <v>6765056</v>
+        <v>6765045</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,11 +2615,6 @@
       <c r="AB19" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2646,7 +2641,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129147447</v>
+        <v>129148629</v>
       </c>
       <c r="B20" t="n">
         <v>79039</v>
@@ -2681,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491606</v>
+        <v>491834</v>
       </c>
       <c r="R20" t="n">
-        <v>6765045</v>
+        <v>6765056</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2727,6 +2722,11 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129146961</v>
+        <v>129146427</v>
       </c>
       <c r="B24" t="n">
-        <v>57885</v>
+        <v>57722</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3085,27 +3085,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491652</v>
+        <v>491626</v>
       </c>
       <c r="R24" t="n">
-        <v>6765086</v>
+        <v>6765093</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,10 +3186,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129146427</v>
+        <v>129146961</v>
       </c>
       <c r="B25" t="n">
-        <v>57722</v>
+        <v>57885</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3197,27 +3197,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491626</v>
+        <v>491652</v>
       </c>
       <c r="R25" t="n">
-        <v>6765093</v>
+        <v>6765086</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3868,7 +3868,7 @@
         <v>129147916</v>
       </c>
       <c r="B31" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4094,10 +4094,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129149409</v>
+        <v>129146351</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4105,37 +4105,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491784</v>
+        <v>491626</v>
       </c>
       <c r="R33" t="n">
-        <v>6765153</v>
+        <v>6765093</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4167,7 +4169,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4177,12 +4179,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter samt miljöbilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4191,7 +4188,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4210,10 +4206,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129146351</v>
+        <v>129149409</v>
       </c>
       <c r="B34" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4221,39 +4217,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491626</v>
+        <v>491784</v>
       </c>
       <c r="R34" t="n">
-        <v>6765093</v>
+        <v>6765153</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4285,7 +4279,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4295,7 +4289,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter samt miljöbilder</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4304,6 +4303,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4999,10 +4999,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129148972</v>
+        <v>129146529</v>
       </c>
       <c r="B41" t="n">
-        <v>91533</v>
+        <v>57722</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5010,37 +5010,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491791</v>
+        <v>491659</v>
       </c>
       <c r="R41" t="n">
-        <v>6765007</v>
+        <v>6765108</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5072,7 +5074,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5082,12 +5084,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Vedsvamp, granlåga, 3 bilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5096,7 +5093,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5115,10 +5111,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129146529</v>
+        <v>129148972</v>
       </c>
       <c r="B42" t="n">
-        <v>57722</v>
+        <v>91540</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5126,39 +5122,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491659</v>
+        <v>491791</v>
       </c>
       <c r="R42" t="n">
-        <v>6765108</v>
+        <v>6765007</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5190,7 +5184,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5200,7 +5194,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Vedsvamp, granlåga, 3 bilder</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5209,6 +5208,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5344,7 +5344,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129148485</v>
+        <v>129148524</v>
       </c>
       <c r="B44" t="n">
         <v>79039</v>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491823</v>
+        <v>491825</v>
       </c>
       <c r="R44" t="n">
-        <v>6764963</v>
+        <v>6765020</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
+          <t>I gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,7 +5456,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129148524</v>
+        <v>129148485</v>
       </c>
       <c r="B45" t="n">
         <v>79039</v>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491825</v>
+        <v>491823</v>
       </c>
       <c r="R45" t="n">
-        <v>6765020</v>
+        <v>6764963</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>I gran</t>
+          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>129147059</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>129147386</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>129147406</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>129145482</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>129147986</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>129146972</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>129147806</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>129147148</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>129146949</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>129147447</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>129148629</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>129145950</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>129147379</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>129146427</v>
       </c>
       <c r="B24" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>129146961</v>
       </c>
       <c r="B25" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>129148592</v>
       </c>
       <c r="B26" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>129149092</v>
       </c>
       <c r="B27" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>129149060</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>129149167</v>
       </c>
       <c r="B29" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>129147300</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129147916</v>
       </c>
       <c r="B31" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>129148872</v>
       </c>
       <c r="B32" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4094,10 +4094,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129146351</v>
+        <v>129149409</v>
       </c>
       <c r="B33" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4105,39 +4105,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491626</v>
+        <v>491784</v>
       </c>
       <c r="R33" t="n">
-        <v>6765093</v>
+        <v>6765153</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4169,7 +4167,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4179,7 +4177,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter samt miljöbilder</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4188,6 +4191,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4206,10 +4210,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129149409</v>
+        <v>129146351</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4217,37 +4221,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491784</v>
+        <v>491626</v>
       </c>
       <c r="R34" t="n">
-        <v>6765153</v>
+        <v>6765093</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4279,7 +4285,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4289,12 +4295,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter samt miljöbilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4303,7 +4304,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>129148685</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>129148571</v>
       </c>
       <c r="B36" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>129148408</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>129147170</v>
       </c>
       <c r="B38" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>129148866</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>129148294</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4999,10 +4999,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129146529</v>
+        <v>129148972</v>
       </c>
       <c r="B41" t="n">
-        <v>57722</v>
+        <v>91542</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5010,39 +5010,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491659</v>
+        <v>491791</v>
       </c>
       <c r="R41" t="n">
-        <v>6765108</v>
+        <v>6765007</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5074,7 +5072,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5084,7 +5082,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Vedsvamp, granlåga, 3 bilder</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5093,6 +5096,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5111,10 +5115,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129148972</v>
+        <v>129146529</v>
       </c>
       <c r="B42" t="n">
-        <v>91540</v>
+        <v>57724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5122,37 +5126,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491791</v>
+        <v>491659</v>
       </c>
       <c r="R42" t="n">
-        <v>6765007</v>
+        <v>6765108</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5184,7 +5190,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5194,12 +5200,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Vedsvamp, granlåga, 3 bilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5208,7 +5209,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5230,7 +5230,7 @@
         <v>129148942</v>
       </c>
       <c r="B43" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>129148524</v>
       </c>
       <c r="B44" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>129148485</v>
       </c>
       <c r="B45" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>129145705</v>
       </c>
       <c r="B46" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -2753,32 +2753,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129145950</v>
+        <v>129146456</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2860,32 +2860,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129146456</v>
+        <v>129145950</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129147170</v>
+        <v>129148866</v>
       </c>
       <c r="B38" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,39 +4669,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491656</v>
+        <v>491782</v>
       </c>
       <c r="R38" t="n">
-        <v>6765038</v>
+        <v>6765017</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4733,7 +4728,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4743,12 +4738,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Bild 3 spillkr</t>
+          <t>Rikligt i en radie av 30 meter</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4775,10 +4770,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129148866</v>
+        <v>129147170</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4786,34 +4781,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491782</v>
+        <v>491656</v>
       </c>
       <c r="R39" t="n">
-        <v>6765017</v>
+        <v>6765038</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 30 meter</t>
+          <t>Bild 3 spillkr</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5344,10 +5344,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129148524</v>
+        <v>129145705</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5355,34 +5355,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491825</v>
+        <v>491605</v>
       </c>
       <c r="R44" t="n">
-        <v>6765020</v>
+        <v>6765075</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5425,11 +5430,6 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>I gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,7 +5456,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129148485</v>
+        <v>129148524</v>
       </c>
       <c r="B45" t="n">
         <v>79041</v>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491823</v>
+        <v>491825</v>
       </c>
       <c r="R45" t="n">
-        <v>6764963</v>
+        <v>6765020</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
+          <t>I gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5568,10 +5568,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129145705</v>
+        <v>129148485</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5579,39 +5579,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491605</v>
+        <v>491823</v>
       </c>
       <c r="R46" t="n">
-        <v>6765075</v>
+        <v>6764963</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5654,6 +5649,11 @@
       <c r="AB46" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -5344,10 +5344,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129145705</v>
+        <v>129148524</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5355,39 +5355,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491605</v>
+        <v>491825</v>
       </c>
       <c r="R44" t="n">
-        <v>6765075</v>
+        <v>6765020</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5430,6 +5425,11 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>I gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,7 +5456,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129148524</v>
+        <v>129148485</v>
       </c>
       <c r="B45" t="n">
         <v>79041</v>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491825</v>
+        <v>491823</v>
       </c>
       <c r="R45" t="n">
-        <v>6765020</v>
+        <v>6764963</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>I gran</t>
+          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5568,10 +5568,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129148485</v>
+        <v>129145705</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5579,34 +5579,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491823</v>
+        <v>491605</v>
       </c>
       <c r="R46" t="n">
-        <v>6764963</v>
+        <v>6765075</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5649,11 +5654,6 @@
       <c r="AB46" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -2753,32 +2753,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129146456</v>
+        <v>129145950</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2860,32 +2860,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129145950</v>
+        <v>129146456</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3868,7 +3868,7 @@
         <v>129147916</v>
       </c>
       <c r="B31" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4094,10 +4094,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129149409</v>
+        <v>129146351</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4105,37 +4105,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491784</v>
+        <v>491626</v>
       </c>
       <c r="R33" t="n">
-        <v>6765153</v>
+        <v>6765093</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4167,7 +4169,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4177,12 +4179,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter samt miljöbilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4191,7 +4188,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4210,10 +4206,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129146351</v>
+        <v>129149409</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4221,39 +4217,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491626</v>
+        <v>491784</v>
       </c>
       <c r="R34" t="n">
-        <v>6765093</v>
+        <v>6765153</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4285,7 +4279,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4295,7 +4289,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter samt miljöbilder</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4304,6 +4303,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4999,10 +4999,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129148972</v>
+        <v>129146529</v>
       </c>
       <c r="B41" t="n">
-        <v>91542</v>
+        <v>57724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5010,37 +5010,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491791</v>
+        <v>491659</v>
       </c>
       <c r="R41" t="n">
-        <v>6765007</v>
+        <v>6765108</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5072,7 +5074,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5082,12 +5084,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Vedsvamp, granlåga, 3 bilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5096,7 +5093,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5115,10 +5111,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129146529</v>
+        <v>129148972</v>
       </c>
       <c r="B42" t="n">
-        <v>57724</v>
+        <v>91540</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5126,39 +5122,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491659</v>
+        <v>491791</v>
       </c>
       <c r="R42" t="n">
-        <v>6765108</v>
+        <v>6765007</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5190,7 +5184,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5200,7 +5194,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Vedsvamp, granlåga, 3 bilder</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5209,6 +5208,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129147406</v>
+        <v>129145482</v>
       </c>
       <c r="B12" t="n">
         <v>79041</v>
@@ -1823,7 +1823,7 @@
         <v>491605</v>
       </c>
       <c r="R12" t="n">
-        <v>6765052</v>
+        <v>6765075</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129145482</v>
+        <v>129147406</v>
       </c>
       <c r="B13" t="n">
         <v>79041</v>
@@ -1930,7 +1930,7 @@
         <v>491605</v>
       </c>
       <c r="R13" t="n">
-        <v>6765075</v>
+        <v>6765052</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -3868,7 +3868,7 @@
         <v>129147916</v>
       </c>
       <c r="B31" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129148571</v>
+        <v>129148408</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491827</v>
+        <v>491876</v>
       </c>
       <c r="R36" t="n">
-        <v>6765046</v>
+        <v>6764940</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Rikligt i en radie av ca 50 meter Ca tio bilder tagna</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4546,7 +4546,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129148408</v>
+        <v>129148571</v>
       </c>
       <c r="B37" t="n">
         <v>79041</v>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491876</v>
+        <v>491827</v>
       </c>
       <c r="R37" t="n">
-        <v>6764940</v>
+        <v>6765046</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter Ca tio bilder tagna</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129145482</v>
+        <v>129147406</v>
       </c>
       <c r="B12" t="n">
         <v>79041</v>
@@ -1823,7 +1823,7 @@
         <v>491605</v>
       </c>
       <c r="R12" t="n">
-        <v>6765075</v>
+        <v>6765052</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129147406</v>
+        <v>129145482</v>
       </c>
       <c r="B13" t="n">
         <v>79041</v>
@@ -1930,7 +1930,7 @@
         <v>491605</v>
       </c>
       <c r="R13" t="n">
-        <v>6765052</v>
+        <v>6765075</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -3868,7 +3868,7 @@
         <v>129147916</v>
       </c>
       <c r="B31" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4094,10 +4094,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129146351</v>
+        <v>129149409</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4105,39 +4105,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491626</v>
+        <v>491784</v>
       </c>
       <c r="R33" t="n">
-        <v>6765093</v>
+        <v>6765153</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4169,7 +4167,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4179,7 +4177,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter samt miljöbilder</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4188,6 +4191,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4206,10 +4210,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129149409</v>
+        <v>129146351</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4217,37 +4221,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491784</v>
+        <v>491626</v>
       </c>
       <c r="R34" t="n">
-        <v>6765153</v>
+        <v>6765093</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4279,7 +4285,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4289,12 +4295,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter samt miljöbilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4303,7 +4304,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129148408</v>
+        <v>129148571</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491876</v>
+        <v>491827</v>
       </c>
       <c r="R36" t="n">
-        <v>6764940</v>
+        <v>6765046</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter Ca tio bilder tagna</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4546,7 +4546,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129148571</v>
+        <v>129148408</v>
       </c>
       <c r="B37" t="n">
         <v>79041</v>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491827</v>
+        <v>491876</v>
       </c>
       <c r="R37" t="n">
-        <v>6765046</v>
+        <v>6764940</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Rikligt i en radie av ca 50 meter Ca tio bilder tagna</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4658,10 +4658,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129148866</v>
+        <v>129147170</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,34 +4669,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491782</v>
+        <v>491656</v>
       </c>
       <c r="R38" t="n">
-        <v>6765017</v>
+        <v>6765038</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4728,7 +4733,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4738,12 +4743,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 30 meter</t>
+          <t>Bild 3 spillkr</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4770,10 +4775,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129147170</v>
+        <v>129148866</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4781,39 +4786,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491656</v>
+        <v>491782</v>
       </c>
       <c r="R39" t="n">
-        <v>6765038</v>
+        <v>6765017</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Bild 3 spillkr</t>
+          <t>Rikligt i en radie av 30 meter</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4999,10 +4999,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129146529</v>
+        <v>129148972</v>
       </c>
       <c r="B41" t="n">
-        <v>57724</v>
+        <v>91540</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5010,39 +5010,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491659</v>
+        <v>491791</v>
       </c>
       <c r="R41" t="n">
-        <v>6765108</v>
+        <v>6765007</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5074,7 +5072,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5084,7 +5082,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Vedsvamp, granlåga, 3 bilder</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5093,6 +5096,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5111,10 +5115,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129148972</v>
+        <v>129146529</v>
       </c>
       <c r="B42" t="n">
-        <v>91540</v>
+        <v>57724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5122,37 +5126,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491791</v>
+        <v>491659</v>
       </c>
       <c r="R42" t="n">
-        <v>6765007</v>
+        <v>6765108</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5184,7 +5190,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5194,12 +5200,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Vedsvamp, granlåga, 3 bilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5208,7 +5209,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>129147059</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>129147386</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>129147406</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>129145482</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>129147986</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>129146972</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>129147806</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>129147148</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>129146949</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>129147447</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>129148629</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>129145950</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>129147379</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129146427</v>
+        <v>129146961</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3085,27 +3085,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491626</v>
+        <v>491652</v>
       </c>
       <c r="R24" t="n">
-        <v>6765093</v>
+        <v>6765086</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,10 +3186,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129146961</v>
+        <v>129146427</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3197,27 +3197,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491652</v>
+        <v>491626</v>
       </c>
       <c r="R25" t="n">
-        <v>6765086</v>
+        <v>6765093</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3413,7 +3413,7 @@
         <v>129149092</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>129149060</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>129147300</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129147916</v>
       </c>
       <c r="B31" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4094,10 +4094,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129149409</v>
+        <v>129146351</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4105,37 +4105,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491784</v>
+        <v>491626</v>
       </c>
       <c r="R33" t="n">
-        <v>6765153</v>
+        <v>6765093</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4167,7 +4169,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4177,12 +4179,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter samt miljöbilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4191,7 +4188,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4210,10 +4206,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129146351</v>
+        <v>129149409</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4221,39 +4217,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491626</v>
+        <v>491784</v>
       </c>
       <c r="R34" t="n">
-        <v>6765093</v>
+        <v>6765153</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4285,7 +4279,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4295,7 +4289,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter samt miljöbilder</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4304,6 +4303,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>129148685</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>129148571</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>129148408</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129147170</v>
+        <v>129148866</v>
       </c>
       <c r="B38" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,39 +4669,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491656</v>
+        <v>491782</v>
       </c>
       <c r="R38" t="n">
-        <v>6765038</v>
+        <v>6765017</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4733,7 +4728,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4743,12 +4738,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Bild 3 spillkr</t>
+          <t>Rikligt i en radie av 30 meter</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4775,10 +4770,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129148866</v>
+        <v>129147170</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4786,34 +4781,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491782</v>
+        <v>491656</v>
       </c>
       <c r="R39" t="n">
-        <v>6765017</v>
+        <v>6765038</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 30 meter</t>
+          <t>Bild 3 spillkr</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4890,7 +4890,7 @@
         <v>129148294</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4999,10 +4999,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129148972</v>
+        <v>129146529</v>
       </c>
       <c r="B41" t="n">
-        <v>91540</v>
+        <v>57724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5010,37 +5010,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491791</v>
+        <v>491659</v>
       </c>
       <c r="R41" t="n">
-        <v>6765007</v>
+        <v>6765108</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5072,7 +5074,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5082,12 +5084,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Vedsvamp, granlåga, 3 bilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5096,7 +5093,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5115,10 +5111,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129146529</v>
+        <v>129148972</v>
       </c>
       <c r="B42" t="n">
-        <v>57724</v>
+        <v>91543</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5126,39 +5122,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491659</v>
+        <v>491791</v>
       </c>
       <c r="R42" t="n">
-        <v>6765108</v>
+        <v>6765007</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5190,7 +5184,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5200,7 +5194,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Vedsvamp, granlåga, 3 bilder</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5209,6 +5208,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5347,7 +5347,7 @@
         <v>129148524</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>129148485</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -4094,10 +4094,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129146351</v>
+        <v>129149409</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4105,39 +4105,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491626</v>
+        <v>491784</v>
       </c>
       <c r="R33" t="n">
-        <v>6765093</v>
+        <v>6765153</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4169,7 +4167,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4179,7 +4177,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter samt miljöbilder</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4188,6 +4191,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4206,10 +4210,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129149409</v>
+        <v>129146351</v>
       </c>
       <c r="B34" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4217,37 +4221,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491784</v>
+        <v>491626</v>
       </c>
       <c r="R34" t="n">
-        <v>6765153</v>
+        <v>6765093</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4279,7 +4285,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4289,12 +4295,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter samt miljöbilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4303,7 +4304,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>129147059</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>129147386</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>129147406</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>129145482</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>129147986</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>129146972</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>129147806</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>129147148</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>129146949</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>129147447</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>129148629</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2753,32 +2753,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129145950</v>
+        <v>129146456</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2860,32 +2860,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129146456</v>
+        <v>129145950</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2970,7 +2970,7 @@
         <v>129147379</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129146961</v>
+        <v>129146427</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3085,27 +3085,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491652</v>
+        <v>491626</v>
       </c>
       <c r="R24" t="n">
-        <v>6765086</v>
+        <v>6765093</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,10 +3186,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129146427</v>
+        <v>129146961</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3197,27 +3197,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491626</v>
+        <v>491652</v>
       </c>
       <c r="R25" t="n">
-        <v>6765093</v>
+        <v>6765086</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3413,7 +3413,7 @@
         <v>129149092</v>
       </c>
       <c r="B27" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>129149060</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>129147300</v>
       </c>
       <c r="B30" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129147916</v>
       </c>
       <c r="B31" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4094,10 +4094,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129149409</v>
+        <v>129146351</v>
       </c>
       <c r="B33" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4105,37 +4105,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491784</v>
+        <v>491626</v>
       </c>
       <c r="R33" t="n">
-        <v>6765153</v>
+        <v>6765093</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4167,7 +4169,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4177,12 +4179,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter samt miljöbilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4191,7 +4188,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4210,10 +4206,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129146351</v>
+        <v>129149409</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4221,39 +4217,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491626</v>
+        <v>491784</v>
       </c>
       <c r="R34" t="n">
-        <v>6765093</v>
+        <v>6765153</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4285,7 +4279,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4295,7 +4289,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter samt miljöbilder</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4304,6 +4303,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>129148685</v>
       </c>
       <c r="B35" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>129148571</v>
       </c>
       <c r="B36" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>129148408</v>
       </c>
       <c r="B37" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129148866</v>
+        <v>129147170</v>
       </c>
       <c r="B38" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,34 +4669,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491782</v>
+        <v>491656</v>
       </c>
       <c r="R38" t="n">
-        <v>6765017</v>
+        <v>6765038</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4728,7 +4733,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4738,12 +4743,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 30 meter</t>
+          <t>Bild 3 spillkr</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4770,10 +4775,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129147170</v>
+        <v>129148866</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4781,39 +4786,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491656</v>
+        <v>491782</v>
       </c>
       <c r="R39" t="n">
-        <v>6765038</v>
+        <v>6765017</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Bild 3 spillkr</t>
+          <t>Rikligt i en radie av 30 meter</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4890,7 +4890,7 @@
         <v>129148294</v>
       </c>
       <c r="B40" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4999,10 +4999,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129146529</v>
+        <v>129148972</v>
       </c>
       <c r="B41" t="n">
-        <v>57724</v>
+        <v>91545</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5010,39 +5010,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491659</v>
+        <v>491791</v>
       </c>
       <c r="R41" t="n">
-        <v>6765108</v>
+        <v>6765007</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5074,7 +5072,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5084,7 +5082,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Vedsvamp, granlåga, 3 bilder</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5093,6 +5096,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5111,10 +5115,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129148972</v>
+        <v>129146529</v>
       </c>
       <c r="B42" t="n">
-        <v>91543</v>
+        <v>57724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5122,37 +5126,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491791</v>
+        <v>491659</v>
       </c>
       <c r="R42" t="n">
-        <v>6765007</v>
+        <v>6765108</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5184,7 +5190,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5194,12 +5200,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Vedsvamp, granlåga, 3 bilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5208,7 +5209,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5344,10 +5344,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129148524</v>
+        <v>129145705</v>
       </c>
       <c r="B44" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5355,34 +5355,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491825</v>
+        <v>491605</v>
       </c>
       <c r="R44" t="n">
-        <v>6765020</v>
+        <v>6765075</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5425,11 +5430,6 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>I gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,10 +5456,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129148485</v>
+        <v>129148524</v>
       </c>
       <c r="B45" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491823</v>
+        <v>491825</v>
       </c>
       <c r="R45" t="n">
-        <v>6764963</v>
+        <v>6765020</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
+          <t>I gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5568,10 +5568,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129145705</v>
+        <v>129148485</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5579,39 +5579,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491605</v>
+        <v>491823</v>
       </c>
       <c r="R46" t="n">
-        <v>6765075</v>
+        <v>6764963</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5654,6 +5649,11 @@
       <c r="AB46" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -2753,32 +2753,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129146456</v>
+        <v>129145950</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2860,32 +2860,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129145950</v>
+        <v>129146456</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129146427</v>
+        <v>129146961</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3085,27 +3085,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491626</v>
+        <v>491652</v>
       </c>
       <c r="R24" t="n">
-        <v>6765093</v>
+        <v>6765086</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,10 +3186,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129146961</v>
+        <v>129146427</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3197,27 +3197,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491652</v>
+        <v>491626</v>
       </c>
       <c r="R25" t="n">
-        <v>6765086</v>
+        <v>6765093</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3868,7 +3868,7 @@
         <v>129147916</v>
       </c>
       <c r="B31" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4999,10 +4999,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129148972</v>
+        <v>129146529</v>
       </c>
       <c r="B41" t="n">
-        <v>91545</v>
+        <v>57724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5010,37 +5010,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491791</v>
+        <v>491659</v>
       </c>
       <c r="R41" t="n">
-        <v>6765007</v>
+        <v>6765108</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5072,7 +5074,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5082,12 +5084,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Vedsvamp, granlåga, 3 bilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5096,7 +5093,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5115,10 +5111,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129146529</v>
+        <v>129148972</v>
       </c>
       <c r="B42" t="n">
-        <v>57724</v>
+        <v>91549</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5126,39 +5122,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491659</v>
+        <v>491791</v>
       </c>
       <c r="R42" t="n">
-        <v>6765108</v>
+        <v>6765007</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5190,7 +5184,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5200,7 +5194,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Vedsvamp, granlåga, 3 bilder</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5209,6 +5208,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5344,10 +5344,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129145705</v>
+        <v>129148524</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5355,39 +5355,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491605</v>
+        <v>491825</v>
       </c>
       <c r="R44" t="n">
-        <v>6765075</v>
+        <v>6765020</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5430,6 +5425,11 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>I gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,10 +5456,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129148524</v>
+        <v>129145705</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5467,34 +5467,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491825</v>
+        <v>491605</v>
       </c>
       <c r="R45" t="n">
-        <v>6765020</v>
+        <v>6765075</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5537,11 +5542,6 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>I gran</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129146961</v>
+        <v>129146427</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3085,27 +3085,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491652</v>
+        <v>491626</v>
       </c>
       <c r="R24" t="n">
-        <v>6765086</v>
+        <v>6765093</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,10 +3186,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129146427</v>
+        <v>129146961</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3197,27 +3197,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491626</v>
+        <v>491652</v>
       </c>
       <c r="R25" t="n">
-        <v>6765093</v>
+        <v>6765086</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3868,7 +3868,7 @@
         <v>129147916</v>
       </c>
       <c r="B31" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4094,10 +4094,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129146351</v>
+        <v>129149409</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4105,39 +4105,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491626</v>
+        <v>491784</v>
       </c>
       <c r="R33" t="n">
-        <v>6765093</v>
+        <v>6765153</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4169,7 +4167,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4179,7 +4177,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter samt miljöbilder</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4188,6 +4191,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4206,10 +4210,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129149409</v>
+        <v>129146351</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4217,37 +4221,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491784</v>
+        <v>491626</v>
       </c>
       <c r="R34" t="n">
-        <v>6765153</v>
+        <v>6765093</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4279,7 +4285,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4289,12 +4295,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter samt miljöbilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4303,7 +4304,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129147170</v>
+        <v>129148866</v>
       </c>
       <c r="B38" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,39 +4669,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491656</v>
+        <v>491782</v>
       </c>
       <c r="R38" t="n">
-        <v>6765038</v>
+        <v>6765017</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4733,7 +4728,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4743,12 +4738,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Bild 3 spillkr</t>
+          <t>Rikligt i en radie av 30 meter</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4775,10 +4770,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129148866</v>
+        <v>129147170</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4786,34 +4781,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491782</v>
+        <v>491656</v>
       </c>
       <c r="R39" t="n">
-        <v>6765017</v>
+        <v>6765038</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 30 meter</t>
+          <t>Bild 3 spillkr</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5114,7 +5114,7 @@
         <v>129148972</v>
       </c>
       <c r="B42" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5456,10 +5456,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129145705</v>
+        <v>129148485</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5467,39 +5467,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491605</v>
+        <v>491823</v>
       </c>
       <c r="R45" t="n">
-        <v>6765075</v>
+        <v>6764963</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5542,6 +5537,11 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5568,10 +5568,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129148485</v>
+        <v>129145705</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5579,34 +5579,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491823</v>
+        <v>491605</v>
       </c>
       <c r="R46" t="n">
-        <v>6764963</v>
+        <v>6765075</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5649,11 +5654,6 @@
       <c r="AB46" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -2534,7 +2534,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129147447</v>
+        <v>129148629</v>
       </c>
       <c r="B19" t="n">
         <v>79044</v>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491606</v>
+        <v>491834</v>
       </c>
       <c r="R19" t="n">
-        <v>6765045</v>
+        <v>6765056</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,6 +2615,11 @@
       <c r="AB19" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2641,7 +2646,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129148629</v>
+        <v>129147447</v>
       </c>
       <c r="B20" t="n">
         <v>79044</v>
@@ -2676,10 +2681,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491834</v>
+        <v>491606</v>
       </c>
       <c r="R20" t="n">
-        <v>6765056</v>
+        <v>6765045</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2722,11 +2727,6 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -4658,10 +4658,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129148866</v>
+        <v>129147170</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,34 +4669,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491782</v>
+        <v>491656</v>
       </c>
       <c r="R38" t="n">
-        <v>6765017</v>
+        <v>6765038</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4728,7 +4733,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4738,12 +4743,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 30 meter</t>
+          <t>Bild 3 spillkr</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4770,10 +4775,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129147170</v>
+        <v>129148866</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4781,39 +4786,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491656</v>
+        <v>491782</v>
       </c>
       <c r="R39" t="n">
-        <v>6765038</v>
+        <v>6765017</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Bild 3 spillkr</t>
+          <t>Rikligt i en radie av 30 meter</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4999,10 +4999,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129146529</v>
+        <v>129148972</v>
       </c>
       <c r="B41" t="n">
-        <v>57724</v>
+        <v>91550</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5010,39 +5010,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491659</v>
+        <v>491791</v>
       </c>
       <c r="R41" t="n">
-        <v>6765108</v>
+        <v>6765007</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5074,7 +5072,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5084,7 +5082,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Vedsvamp, granlåga, 3 bilder</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5093,6 +5096,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5111,10 +5115,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129148972</v>
+        <v>129146529</v>
       </c>
       <c r="B42" t="n">
-        <v>91550</v>
+        <v>57724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5122,37 +5126,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491791</v>
+        <v>491659</v>
       </c>
       <c r="R42" t="n">
-        <v>6765007</v>
+        <v>6765108</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5184,7 +5190,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5194,12 +5200,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Vedsvamp, granlåga, 3 bilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5208,7 +5209,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5456,10 +5456,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129148485</v>
+        <v>129145705</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5467,34 +5467,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491823</v>
+        <v>491605</v>
       </c>
       <c r="R45" t="n">
-        <v>6764963</v>
+        <v>6765075</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5537,11 +5542,6 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5568,10 +5568,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129145705</v>
+        <v>129148485</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5579,39 +5579,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491605</v>
+        <v>491823</v>
       </c>
       <c r="R46" t="n">
-        <v>6765075</v>
+        <v>6764963</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5654,6 +5649,11 @@
       <c r="AB46" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -2106,7 +2106,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129146972</v>
+        <v>129146989</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2534,7 +2534,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129148629</v>
+        <v>129147447</v>
       </c>
       <c r="B19" t="n">
         <v>79044</v>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491834</v>
+        <v>491606</v>
       </c>
       <c r="R19" t="n">
-        <v>6765056</v>
+        <v>6765045</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,11 +2615,6 @@
       <c r="AB19" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2646,7 +2641,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129147447</v>
+        <v>129148629</v>
       </c>
       <c r="B20" t="n">
         <v>79044</v>
@@ -2681,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491606</v>
+        <v>491834</v>
       </c>
       <c r="R20" t="n">
-        <v>6765045</v>
+        <v>6765056</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2727,6 +2722,11 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2753,32 +2753,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129145950</v>
+        <v>129146456</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2860,32 +2860,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129146456</v>
+        <v>129145950</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129146427</v>
+        <v>129146961</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3085,27 +3085,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491626</v>
+        <v>491652</v>
       </c>
       <c r="R24" t="n">
-        <v>6765093</v>
+        <v>6765086</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,10 +3186,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129146961</v>
+        <v>129146427</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3197,27 +3197,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491652</v>
+        <v>491626</v>
       </c>
       <c r="R25" t="n">
-        <v>6765086</v>
+        <v>6765093</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -1571,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129147059</v>
+        <v>129147386</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491660</v>
+        <v>491600</v>
       </c>
       <c r="R10" t="n">
-        <v>6765053</v>
+        <v>6765059</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129147386</v>
+        <v>129147059</v>
       </c>
       <c r="B11" t="n">
         <v>79044</v>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491600</v>
+        <v>491660</v>
       </c>
       <c r="R11" t="n">
-        <v>6765059</v>
+        <v>6765053</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129147406</v>
+        <v>129145482</v>
       </c>
       <c r="B12" t="n">
         <v>79044</v>
@@ -1823,7 +1823,7 @@
         <v>491605</v>
       </c>
       <c r="R12" t="n">
-        <v>6765052</v>
+        <v>6765075</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129145482</v>
+        <v>129147406</v>
       </c>
       <c r="B13" t="n">
         <v>79044</v>
@@ -1930,7 +1930,7 @@
         <v>491605</v>
       </c>
       <c r="R13" t="n">
-        <v>6765075</v>
+        <v>6765052</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2106,7 +2106,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129146989</v>
+        <v>129146972</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129147148</v>
+        <v>129146949</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491656</v>
+        <v>491660</v>
       </c>
       <c r="R17" t="n">
-        <v>6765038</v>
+        <v>6765085</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2427,7 +2427,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129146949</v>
+        <v>129147148</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491660</v>
+        <v>491656</v>
       </c>
       <c r="R18" t="n">
-        <v>6765085</v>
+        <v>6765038</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2753,32 +2753,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129146456</v>
+        <v>129145950</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2860,32 +2860,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129145950</v>
+        <v>129146456</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129146961</v>
+        <v>129146427</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3085,27 +3085,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491652</v>
+        <v>491626</v>
       </c>
       <c r="R24" t="n">
-        <v>6765086</v>
+        <v>6765093</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,10 +3186,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129146427</v>
+        <v>129146961</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3197,27 +3197,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491626</v>
+        <v>491652</v>
       </c>
       <c r="R25" t="n">
-        <v>6765093</v>
+        <v>6765086</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3868,7 +3868,7 @@
         <v>129147916</v>
       </c>
       <c r="B31" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129147170</v>
+        <v>129148866</v>
       </c>
       <c r="B38" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,39 +4669,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491656</v>
+        <v>491782</v>
       </c>
       <c r="R38" t="n">
-        <v>6765038</v>
+        <v>6765017</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4733,7 +4728,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4743,12 +4738,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Bild 3 spillkr</t>
+          <t>Rikligt i en radie av 30 meter</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4775,10 +4770,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129148866</v>
+        <v>129147170</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4786,34 +4781,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491782</v>
+        <v>491656</v>
       </c>
       <c r="R39" t="n">
-        <v>6765017</v>
+        <v>6765038</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 30 meter</t>
+          <t>Bild 3 spillkr</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5002,7 +5002,7 @@
         <v>129148972</v>
       </c>
       <c r="B41" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129148524</v>
+        <v>129148485</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491825</v>
+        <v>491823</v>
       </c>
       <c r="R44" t="n">
-        <v>6765020</v>
+        <v>6764963</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>I gran</t>
+          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,10 +5456,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129145705</v>
+        <v>129148524</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5467,39 +5467,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491605</v>
+        <v>491825</v>
       </c>
       <c r="R45" t="n">
-        <v>6765075</v>
+        <v>6765020</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5542,6 +5537,11 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>I gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5568,10 +5568,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129148485</v>
+        <v>129145705</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5579,34 +5579,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491823</v>
+        <v>491605</v>
       </c>
       <c r="R46" t="n">
-        <v>6764963</v>
+        <v>6765075</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5649,11 +5654,6 @@
       <c r="AB46" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -1571,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129147386</v>
+        <v>129147059</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491600</v>
+        <v>491660</v>
       </c>
       <c r="R10" t="n">
-        <v>6765059</v>
+        <v>6765053</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129147059</v>
+        <v>129147386</v>
       </c>
       <c r="B11" t="n">
         <v>79044</v>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491660</v>
+        <v>491600</v>
       </c>
       <c r="R11" t="n">
-        <v>6765053</v>
+        <v>6765059</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129145482</v>
+        <v>129147406</v>
       </c>
       <c r="B12" t="n">
         <v>79044</v>
@@ -1823,7 +1823,7 @@
         <v>491605</v>
       </c>
       <c r="R12" t="n">
-        <v>6765075</v>
+        <v>6765052</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129147406</v>
+        <v>129145482</v>
       </c>
       <c r="B13" t="n">
         <v>79044</v>
@@ -1930,7 +1930,7 @@
         <v>491605</v>
       </c>
       <c r="R13" t="n">
-        <v>6765052</v>
+        <v>6765075</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129146427</v>
+        <v>129146961</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3085,27 +3085,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491626</v>
+        <v>491652</v>
       </c>
       <c r="R24" t="n">
-        <v>6765093</v>
+        <v>6765086</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,10 +3186,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129146961</v>
+        <v>129146427</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3197,27 +3197,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491652</v>
+        <v>491626</v>
       </c>
       <c r="R25" t="n">
-        <v>6765086</v>
+        <v>6765093</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -2320,7 +2320,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129146949</v>
+        <v>129147148</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491660</v>
+        <v>491656</v>
       </c>
       <c r="R17" t="n">
-        <v>6765085</v>
+        <v>6765038</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2427,7 +2427,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129147148</v>
+        <v>129146949</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491656</v>
+        <v>491660</v>
       </c>
       <c r="R18" t="n">
-        <v>6765038</v>
+        <v>6765085</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129146961</v>
+        <v>129146427</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3085,27 +3085,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491652</v>
+        <v>491626</v>
       </c>
       <c r="R24" t="n">
-        <v>6765086</v>
+        <v>6765093</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,10 +3186,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129146427</v>
+        <v>129146961</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3197,27 +3197,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491626</v>
+        <v>491652</v>
       </c>
       <c r="R25" t="n">
-        <v>6765093</v>
+        <v>6765086</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129148571</v>
+        <v>129148408</v>
       </c>
       <c r="B36" t="n">
         <v>79044</v>
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491827</v>
+        <v>491876</v>
       </c>
       <c r="R36" t="n">
-        <v>6765046</v>
+        <v>6764940</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Rikligt i en radie av ca 50 meter Ca tio bilder tagna</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4546,7 +4546,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129148408</v>
+        <v>129148571</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491876</v>
+        <v>491827</v>
       </c>
       <c r="R37" t="n">
-        <v>6764940</v>
+        <v>6765046</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter Ca tio bilder tagna</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4658,10 +4658,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129148866</v>
+        <v>129147170</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,34 +4669,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491782</v>
+        <v>491656</v>
       </c>
       <c r="R38" t="n">
-        <v>6765017</v>
+        <v>6765038</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4728,7 +4733,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4738,12 +4743,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 30 meter</t>
+          <t>Bild 3 spillkr</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4770,10 +4775,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129147170</v>
+        <v>129148866</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4781,39 +4786,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491656</v>
+        <v>491782</v>
       </c>
       <c r="R39" t="n">
-        <v>6765038</v>
+        <v>6765017</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Bild 3 spillkr</t>
+          <t>Rikligt i en radie av 30 meter</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4999,10 +4999,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129148972</v>
+        <v>129146529</v>
       </c>
       <c r="B41" t="n">
-        <v>91553</v>
+        <v>57724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5010,37 +5010,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491791</v>
+        <v>491659</v>
       </c>
       <c r="R41" t="n">
-        <v>6765007</v>
+        <v>6765108</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5072,7 +5074,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5082,12 +5084,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Vedsvamp, granlåga, 3 bilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5096,7 +5093,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5115,10 +5111,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129146529</v>
+        <v>129148972</v>
       </c>
       <c r="B42" t="n">
-        <v>57724</v>
+        <v>91553</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5126,39 +5122,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491659</v>
+        <v>491791</v>
       </c>
       <c r="R42" t="n">
-        <v>6765108</v>
+        <v>6765007</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5190,7 +5184,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5200,7 +5194,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Vedsvamp, granlåga, 3 bilder</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5209,6 +5208,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5344,7 +5344,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129148485</v>
+        <v>129148524</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491823</v>
+        <v>491825</v>
       </c>
       <c r="R44" t="n">
-        <v>6764963</v>
+        <v>6765020</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
+          <t>I gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,7 +5456,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129148524</v>
+        <v>129148485</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491825</v>
+        <v>491823</v>
       </c>
       <c r="R45" t="n">
-        <v>6765020</v>
+        <v>6764963</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>I gran</t>
+          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129146427</v>
+        <v>129146961</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3085,27 +3085,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491626</v>
+        <v>491652</v>
       </c>
       <c r="R24" t="n">
-        <v>6765093</v>
+        <v>6765086</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,10 +3186,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129146961</v>
+        <v>129146427</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3197,27 +3197,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491652</v>
+        <v>491626</v>
       </c>
       <c r="R25" t="n">
-        <v>6765086</v>
+        <v>6765093</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129148408</v>
+        <v>129148571</v>
       </c>
       <c r="B36" t="n">
         <v>79044</v>
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491876</v>
+        <v>491827</v>
       </c>
       <c r="R36" t="n">
-        <v>6764940</v>
+        <v>6765046</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter Ca tio bilder tagna</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4546,7 +4546,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129148571</v>
+        <v>129148408</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491827</v>
+        <v>491876</v>
       </c>
       <c r="R37" t="n">
-        <v>6765046</v>
+        <v>6764940</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Rikligt i en radie av ca 50 meter Ca tio bilder tagna</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4999,10 +4999,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129146529</v>
+        <v>129148972</v>
       </c>
       <c r="B41" t="n">
-        <v>57724</v>
+        <v>91553</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5010,39 +5010,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491659</v>
+        <v>491791</v>
       </c>
       <c r="R41" t="n">
-        <v>6765108</v>
+        <v>6765007</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5074,7 +5072,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5084,7 +5082,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Vedsvamp, granlåga, 3 bilder</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5093,6 +5096,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5111,10 +5115,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129148972</v>
+        <v>129146529</v>
       </c>
       <c r="B42" t="n">
-        <v>91553</v>
+        <v>57724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5122,37 +5126,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491791</v>
+        <v>491659</v>
       </c>
       <c r="R42" t="n">
-        <v>6765007</v>
+        <v>6765108</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5184,7 +5190,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5194,12 +5200,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Vedsvamp, granlåga, 3 bilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5208,7 +5209,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5344,10 +5344,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129148524</v>
+        <v>129145705</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5355,34 +5355,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491825</v>
+        <v>491605</v>
       </c>
       <c r="R44" t="n">
-        <v>6765020</v>
+        <v>6765075</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5425,11 +5430,6 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>I gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,7 +5456,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129148485</v>
+        <v>129148524</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491823</v>
+        <v>491825</v>
       </c>
       <c r="R45" t="n">
-        <v>6764963</v>
+        <v>6765020</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
+          <t>I gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5568,10 +5568,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129145705</v>
+        <v>129148485</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5579,39 +5579,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491605</v>
+        <v>491823</v>
       </c>
       <c r="R46" t="n">
-        <v>6765075</v>
+        <v>6764963</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5654,6 +5649,11 @@
       <c r="AB46" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -2753,32 +2753,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129145950</v>
+        <v>129146456</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2860,32 +2860,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129146456</v>
+        <v>129145950</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129146961</v>
+        <v>129146427</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3085,27 +3085,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491652</v>
+        <v>491626</v>
       </c>
       <c r="R24" t="n">
-        <v>6765086</v>
+        <v>6765093</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,10 +3186,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129146427</v>
+        <v>129146961</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3197,27 +3197,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491626</v>
+        <v>491652</v>
       </c>
       <c r="R25" t="n">
-        <v>6765093</v>
+        <v>6765086</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -5344,10 +5344,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129145705</v>
+        <v>129148524</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5355,39 +5355,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491605</v>
+        <v>491825</v>
       </c>
       <c r="R44" t="n">
-        <v>6765075</v>
+        <v>6765020</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5430,6 +5425,11 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>I gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,7 +5456,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129148524</v>
+        <v>129148485</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491825</v>
+        <v>491823</v>
       </c>
       <c r="R45" t="n">
-        <v>6765020</v>
+        <v>6764963</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>I gran</t>
+          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5568,10 +5568,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129148485</v>
+        <v>129145705</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5579,34 +5579,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491823</v>
+        <v>491605</v>
       </c>
       <c r="R46" t="n">
-        <v>6764963</v>
+        <v>6765075</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5649,11 +5654,6 @@
       <c r="AB46" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129147406</v>
+        <v>129145482</v>
       </c>
       <c r="B12" t="n">
         <v>79044</v>
@@ -1823,7 +1823,7 @@
         <v>491605</v>
       </c>
       <c r="R12" t="n">
-        <v>6765052</v>
+        <v>6765075</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129145482</v>
+        <v>129147406</v>
       </c>
       <c r="B13" t="n">
         <v>79044</v>
@@ -1930,7 +1930,7 @@
         <v>491605</v>
       </c>
       <c r="R13" t="n">
-        <v>6765075</v>
+        <v>6765052</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2106,7 +2106,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129146972</v>
+        <v>129146989</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129147148</v>
+        <v>129146949</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491656</v>
+        <v>491660</v>
       </c>
       <c r="R17" t="n">
-        <v>6765038</v>
+        <v>6765085</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2427,7 +2427,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129146949</v>
+        <v>129147148</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491660</v>
+        <v>491656</v>
       </c>
       <c r="R18" t="n">
-        <v>6765085</v>
+        <v>6765038</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2534,7 +2534,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129147447</v>
+        <v>129148629</v>
       </c>
       <c r="B19" t="n">
         <v>79044</v>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491606</v>
+        <v>491834</v>
       </c>
       <c r="R19" t="n">
-        <v>6765045</v>
+        <v>6765056</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,6 +2615,11 @@
       <c r="AB19" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2641,7 +2646,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129148629</v>
+        <v>129147447</v>
       </c>
       <c r="B20" t="n">
         <v>79044</v>
@@ -2676,10 +2681,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491834</v>
+        <v>491606</v>
       </c>
       <c r="R20" t="n">
-        <v>6765056</v>
+        <v>6765045</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2722,11 +2727,6 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2753,32 +2753,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129146456</v>
+        <v>129145950</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2860,32 +2860,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129145950</v>
+        <v>129146456</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129148972</v>
+        <v>129146529</v>
       </c>
       <c r="B41" t="n">
-        <v>91553</v>
+        <v>57724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5010,37 +5010,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491791</v>
+        <v>491659</v>
       </c>
       <c r="R41" t="n">
-        <v>6765007</v>
+        <v>6765108</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5072,7 +5074,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5082,12 +5084,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Vedsvamp, granlåga, 3 bilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5096,7 +5093,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5115,10 +5111,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129146529</v>
+        <v>129148972</v>
       </c>
       <c r="B42" t="n">
-        <v>57724</v>
+        <v>91553</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5126,39 +5122,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491659</v>
+        <v>491791</v>
       </c>
       <c r="R42" t="n">
-        <v>6765108</v>
+        <v>6765007</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5190,7 +5184,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5200,7 +5194,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Vedsvamp, granlåga, 3 bilder</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5209,6 +5208,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129147059</v>
+        <v>129147386</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491660</v>
+        <v>491600</v>
       </c>
       <c r="R10" t="n">
-        <v>6765053</v>
+        <v>6765059</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129147386</v>
+        <v>129147059</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491600</v>
+        <v>491660</v>
       </c>
       <c r="R11" t="n">
-        <v>6765059</v>
+        <v>6765053</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
         <v>129145482</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>129147406</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>129147986</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2106,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129146989</v>
+        <v>129146972</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>129147806</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2320,10 +2320,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129146949</v>
+        <v>129147148</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491660</v>
+        <v>491656</v>
       </c>
       <c r="R17" t="n">
-        <v>6765085</v>
+        <v>6765038</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129147148</v>
+        <v>129146949</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491656</v>
+        <v>491660</v>
       </c>
       <c r="R18" t="n">
-        <v>6765038</v>
+        <v>6765085</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2534,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129148629</v>
+        <v>129147447</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491834</v>
+        <v>491606</v>
       </c>
       <c r="R19" t="n">
-        <v>6765056</v>
+        <v>6765045</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,11 +2615,6 @@
       <c r="AB19" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2646,10 +2641,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129147447</v>
+        <v>129148629</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491606</v>
+        <v>491834</v>
       </c>
       <c r="R20" t="n">
-        <v>6765045</v>
+        <v>6765056</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2727,6 +2722,11 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2756,7 +2756,7 @@
         <v>129145950</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>129147379</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>129146427</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>129146961</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>129148592</v>
       </c>
       <c r="B26" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>129149092</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>129149060</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>129149167</v>
       </c>
       <c r="B29" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>129147300</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129147916</v>
       </c>
       <c r="B31" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>129148872</v>
       </c>
       <c r="B32" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>129149409</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>129146351</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>129148685</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4434,10 +4434,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129148571</v>
+        <v>129148408</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491827</v>
+        <v>491876</v>
       </c>
       <c r="R36" t="n">
-        <v>6765046</v>
+        <v>6764940</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Rikligt i en radie av ca 50 meter Ca tio bilder tagna</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4546,10 +4546,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129148408</v>
+        <v>129148571</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491876</v>
+        <v>491827</v>
       </c>
       <c r="R37" t="n">
-        <v>6764940</v>
+        <v>6765046</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter Ca tio bilder tagna</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4658,10 +4658,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129147170</v>
+        <v>129148866</v>
       </c>
       <c r="B38" t="n">
-        <v>57724</v>
+        <v>79070</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,39 +4669,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491656</v>
+        <v>491782</v>
       </c>
       <c r="R38" t="n">
-        <v>6765038</v>
+        <v>6765017</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4733,7 +4728,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4743,12 +4738,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Bild 3 spillkr</t>
+          <t>Rikligt i en radie av 30 meter</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4775,10 +4770,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129148866</v>
+        <v>129147170</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4786,34 +4781,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491782</v>
+        <v>491656</v>
       </c>
       <c r="R39" t="n">
-        <v>6765017</v>
+        <v>6765038</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 30 meter</t>
+          <t>Bild 3 spillkr</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4890,7 +4890,7 @@
         <v>129148294</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4999,10 +4999,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129146529</v>
+        <v>129148972</v>
       </c>
       <c r="B41" t="n">
-        <v>57724</v>
+        <v>91581</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5010,39 +5010,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491659</v>
+        <v>491791</v>
       </c>
       <c r="R41" t="n">
-        <v>6765108</v>
+        <v>6765007</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5074,7 +5072,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5084,7 +5082,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Vedsvamp, granlåga, 3 bilder</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5093,6 +5096,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5111,10 +5115,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129148972</v>
+        <v>129146529</v>
       </c>
       <c r="B42" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5122,37 +5126,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491791</v>
+        <v>491659</v>
       </c>
       <c r="R42" t="n">
-        <v>6765007</v>
+        <v>6765108</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5184,7 +5190,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5194,12 +5200,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Vedsvamp, granlåga, 3 bilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5208,7 +5209,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5230,7 +5230,7 @@
         <v>129148942</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>129148524</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>129148485</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>129145705</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -4434,7 +4434,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129148408</v>
+        <v>129148571</v>
       </c>
       <c r="B36" t="n">
         <v>79070</v>
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491876</v>
+        <v>491827</v>
       </c>
       <c r="R36" t="n">
-        <v>6764940</v>
+        <v>6765046</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter Ca tio bilder tagna</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4546,7 +4546,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129148571</v>
+        <v>129148408</v>
       </c>
       <c r="B37" t="n">
         <v>79070</v>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491827</v>
+        <v>491876</v>
       </c>
       <c r="R37" t="n">
-        <v>6765046</v>
+        <v>6764940</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Rikligt i en radie av ca 50 meter Ca tio bilder tagna</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4658,10 +4658,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129148866</v>
+        <v>129147170</v>
       </c>
       <c r="B38" t="n">
-        <v>79070</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4669,34 +4669,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491782</v>
+        <v>491656</v>
       </c>
       <c r="R38" t="n">
-        <v>6765017</v>
+        <v>6765038</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4728,7 +4733,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4738,12 +4743,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 30 meter</t>
+          <t>Bild 3 spillkr</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4770,10 +4775,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129147170</v>
+        <v>129148866</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4781,39 +4786,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491656</v>
+        <v>491782</v>
       </c>
       <c r="R39" t="n">
-        <v>6765038</v>
+        <v>6765017</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Bild 3 spillkr</t>
+          <t>Rikligt i en radie av 30 meter</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127840593</v>
+        <v>129148972</v>
       </c>
       <c r="B2" t="n">
-        <v>58115</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103001</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491761</v>
+        <v>491791</v>
       </c>
       <c r="R2" t="n">
-        <v>6764863</v>
+        <v>6765007</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +743,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Vedsvamp, granlåga, 3 bilder</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,50 +791,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127840817</v>
+        <v>127840503</v>
       </c>
       <c r="B3" t="n">
-        <v>57682</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491721</v>
+        <v>491796</v>
       </c>
       <c r="R3" t="n">
-        <v>6764946</v>
+        <v>6764811</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -873,6 +872,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>18:37</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,14 +903,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127840503</v>
+        <v>127840604</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -934,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491796</v>
+        <v>491761</v>
       </c>
       <c r="R4" t="n">
-        <v>6764811</v>
+        <v>6764863</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1011,14 +1015,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127840755</v>
+        <v>127840656</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1046,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491757</v>
+        <v>491767</v>
       </c>
       <c r="R5" t="n">
-        <v>6764953</v>
+        <v>6764908</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1123,14 +1127,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127840604</v>
+        <v>127840755</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1158,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491761</v>
+        <v>491757</v>
       </c>
       <c r="R6" t="n">
-        <v>6764863</v>
+        <v>6764953</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1238,11 +1242,11 @@
         <v>127840997</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1350,11 +1354,11 @@
         <v>127841273</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1459,14 +1463,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127840656</v>
+        <v>129145482</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1494,13 +1498,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491767</v>
+        <v>491605</v>
       </c>
       <c r="R9" t="n">
-        <v>6764908</v>
+        <v>6765075</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1524,27 +1528,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:37</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter  5 bilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,14 +1570,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129147386</v>
+        <v>129145950</v>
       </c>
       <c r="B10" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1606,10 +1605,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491600</v>
+        <v>491626</v>
       </c>
       <c r="R10" t="n">
-        <v>6765059</v>
+        <v>6765093</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,14 +1677,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129147059</v>
+        <v>129146949</v>
       </c>
       <c r="B11" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1716,7 +1715,7 @@
         <v>491660</v>
       </c>
       <c r="R11" t="n">
-        <v>6765053</v>
+        <v>6765085</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,14 +1784,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129145482</v>
+        <v>129146972</v>
       </c>
       <c r="B12" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1820,10 +1819,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491605</v>
+        <v>491643</v>
       </c>
       <c r="R12" t="n">
-        <v>6765075</v>
+        <v>6765056</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,14 +1891,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129147406</v>
+        <v>129147059</v>
       </c>
       <c r="B13" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1927,10 +1926,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491605</v>
+        <v>491660</v>
       </c>
       <c r="R13" t="n">
-        <v>6765052</v>
+        <v>6765053</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1999,14 +1998,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129147986</v>
+        <v>129147148</v>
       </c>
       <c r="B14" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2034,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491639</v>
+        <v>491656</v>
       </c>
       <c r="R14" t="n">
-        <v>6764969</v>
+        <v>6765038</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2106,14 +2105,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129146972</v>
+        <v>129147300</v>
       </c>
       <c r="B15" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2141,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491643</v>
+        <v>491625</v>
       </c>
       <c r="R15" t="n">
-        <v>6765056</v>
+        <v>6765040</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,6 +2186,11 @@
       <c r="AB15" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Garn samt 3 miljöbilder</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,14 +2217,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129147806</v>
+        <v>129147358</v>
       </c>
       <c r="B16" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2248,10 +2252,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491641</v>
+        <v>491600</v>
       </c>
       <c r="R16" t="n">
-        <v>6765032</v>
+        <v>6765059</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2294,6 +2298,11 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Garn på 2 stammar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,14 +2329,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129147148</v>
+        <v>129147379</v>
       </c>
       <c r="B17" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2355,10 +2364,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491656</v>
+        <v>491602</v>
       </c>
       <c r="R17" t="n">
-        <v>6765038</v>
+        <v>6765069</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2427,14 +2436,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129146949</v>
+        <v>129147406</v>
       </c>
       <c r="B18" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2462,10 +2471,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491660</v>
+        <v>491605</v>
       </c>
       <c r="R18" t="n">
-        <v>6765085</v>
+        <v>6765052</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2534,14 +2543,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129147447</v>
+        <v>129147438</v>
       </c>
       <c r="B19" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2641,14 +2650,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129148629</v>
+        <v>129147806</v>
       </c>
       <c r="B20" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2676,10 +2685,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491834</v>
+        <v>491641</v>
       </c>
       <c r="R20" t="n">
-        <v>6765056</v>
+        <v>6765032</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2722,11 +2731,6 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2753,14 +2757,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129145950</v>
+        <v>129147986</v>
       </c>
       <c r="B21" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2788,10 +2792,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491626</v>
+        <v>491639</v>
       </c>
       <c r="R21" t="n">
-        <v>6765093</v>
+        <v>6764969</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2860,32 +2864,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129146456</v>
+        <v>129148294</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2895,10 +2899,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491626</v>
+        <v>491862</v>
       </c>
       <c r="R22" t="n">
-        <v>6765093</v>
+        <v>6764868</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2941,6 +2945,11 @@
       <c r="AB22" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2967,14 +2976,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129147379</v>
+        <v>129148408</v>
       </c>
       <c r="B23" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3002,10 +3011,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491602</v>
+        <v>491876</v>
       </c>
       <c r="R23" t="n">
-        <v>6765069</v>
+        <v>6764940</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3048,6 +3057,11 @@
       <c r="AB23" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter Ca tio bilder tagna</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3074,50 +3088,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129146427</v>
+        <v>129148485</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491626</v>
+        <v>491823</v>
       </c>
       <c r="R24" t="n">
-        <v>6765093</v>
+        <v>6764963</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3160,6 +3169,11 @@
       <c r="AB24" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3186,50 +3200,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129146961</v>
+        <v>129148524</v>
       </c>
       <c r="B25" t="n">
-        <v>57890</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491652</v>
+        <v>491825</v>
       </c>
       <c r="R25" t="n">
-        <v>6765086</v>
+        <v>6765020</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3272,6 +3281,11 @@
       <c r="AB25" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3298,40 +3312,35 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129148592</v>
+        <v>129148571</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
@@ -3384,6 +3393,11 @@
       <c r="AB26" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3410,14 +3424,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129149092</v>
+        <v>129148629</v>
       </c>
       <c r="B27" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3445,10 +3459,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491755</v>
+        <v>491834</v>
       </c>
       <c r="R27" t="n">
-        <v>6765029</v>
+        <v>6765056</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3480,7 +3494,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3490,12 +3504,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3522,14 +3536,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129149060</v>
+        <v>129148685</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3551,19 +3565,16 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491763</v>
+        <v>491835</v>
       </c>
       <c r="R28" t="n">
-        <v>6764994</v>
+        <v>6765066</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3595,7 +3606,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3605,12 +3616,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 40 meter 1 bild</t>
+          <t>Rikligt i gran samt tallar 2 bilder</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3619,7 +3630,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3638,53 +3648,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129149167</v>
+        <v>129148866</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491747</v>
+        <v>491782</v>
       </c>
       <c r="R29" t="n">
-        <v>6765080</v>
+        <v>6765017</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3727,6 +3729,11 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 30 meter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3753,14 +3760,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129147300</v>
+        <v>129149060</v>
       </c>
       <c r="B30" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3782,16 +3789,19 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491625</v>
+        <v>491763</v>
       </c>
       <c r="R30" t="n">
-        <v>6765040</v>
+        <v>6764994</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3823,7 +3833,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3833,12 +3843,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Garn samt 3 miljöbilder</t>
+          <t>Rikligt i en radie av 40 meter 1 bild</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3847,6 +3857,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3865,32 +3876,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129147916</v>
+        <v>129149092</v>
       </c>
       <c r="B31" t="n">
-        <v>97627</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3900,10 +3911,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491639</v>
+        <v>491755</v>
       </c>
       <c r="R31" t="n">
-        <v>6764969</v>
+        <v>6765029</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3935,7 +3946,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3945,12 +3956,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Revlummer samt 2 miljöbilder</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3977,50 +3988,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129148872</v>
+        <v>129149409</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491782</v>
+        <v>491784</v>
       </c>
       <c r="R32" t="n">
-        <v>6765017</v>
+        <v>6765153</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4067,7 +4076,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Måttligt till rikligt i en radie av ca 50 meter samt miljöbilder</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4076,6 +4085,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4094,51 +4104,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129149409</v>
+        <v>127840817</v>
       </c>
       <c r="B33" t="n">
-        <v>79070</v>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491784</v>
+        <v>491721</v>
       </c>
       <c r="R33" t="n">
-        <v>6765153</v>
+        <v>6764946</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4162,27 +4174,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter samt miljöbilder</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4191,7 +4198,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4210,27 +4216,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129146351</v>
+        <v>129146427</v>
       </c>
       <c r="B34" t="n">
-        <v>57730</v>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4322,45 +4328,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129148685</v>
+        <v>129146529</v>
       </c>
       <c r="B35" t="n">
-        <v>79070</v>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491835</v>
+        <v>491659</v>
       </c>
       <c r="R35" t="n">
-        <v>6765066</v>
+        <v>6765108</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4403,11 +4414,6 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt i gran samt tallar 2 bilder</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4434,45 +4440,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129148571</v>
+        <v>129147170</v>
       </c>
       <c r="B36" t="n">
-        <v>79070</v>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491827</v>
+        <v>491656</v>
       </c>
       <c r="R36" t="n">
-        <v>6765046</v>
+        <v>6765038</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4519,7 +4530,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Bild 3 spillkr</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4546,45 +4557,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129148408</v>
+        <v>129148592</v>
       </c>
       <c r="B37" t="n">
-        <v>79070</v>
+        <v>57950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491876</v>
+        <v>491827</v>
       </c>
       <c r="R37" t="n">
-        <v>6764940</v>
+        <v>6765046</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4627,11 +4643,6 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter Ca tio bilder tagna</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4658,14 +4669,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129147170</v>
+        <v>129148839</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>57950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4698,10 +4709,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491656</v>
+        <v>491782</v>
       </c>
       <c r="R38" t="n">
-        <v>6765038</v>
+        <v>6765017</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4733,7 +4744,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4743,12 +4754,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Bild 3 spillkr</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4775,45 +4786,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129148866</v>
+        <v>129149167</v>
       </c>
       <c r="B39" t="n">
-        <v>79070</v>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491782</v>
+        <v>491747</v>
       </c>
       <c r="R39" t="n">
-        <v>6765017</v>
+        <v>6765080</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4856,11 +4875,6 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 30 meter</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4887,10 +4901,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129148294</v>
+        <v>129145705</v>
       </c>
       <c r="B40" t="n">
-        <v>79070</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4898,34 +4912,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491862</v>
+        <v>491605</v>
       </c>
       <c r="R40" t="n">
-        <v>6764868</v>
+        <v>6765075</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4968,11 +4987,6 @@
       <c r="AB40" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4999,10 +5013,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129148972</v>
+        <v>129146351</v>
       </c>
       <c r="B41" t="n">
-        <v>91581</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5010,37 +5024,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491791</v>
+        <v>491626</v>
       </c>
       <c r="R41" t="n">
-        <v>6765007</v>
+        <v>6765093</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5072,7 +5088,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5082,12 +5098,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Vedsvamp, granlåga, 3 bilder</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5096,7 +5107,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5115,10 +5125,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129146529</v>
+        <v>129148942</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5126,16 +5136,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5155,10 +5165,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491659</v>
+        <v>491791</v>
       </c>
       <c r="R42" t="n">
-        <v>6765108</v>
+        <v>6765007</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5190,7 +5200,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5200,7 +5210,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5227,10 +5242,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129148942</v>
+        <v>127840593</v>
       </c>
       <c r="B43" t="n">
-        <v>57730</v>
+        <v>58388</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5238,27 +5253,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5267,13 +5282,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491791</v>
+        <v>491761</v>
       </c>
       <c r="R43" t="n">
-        <v>6765007</v>
+        <v>6764863</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5297,27 +5312,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>2 bilder</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5344,10 +5354,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129148524</v>
+        <v>129146961</v>
       </c>
       <c r="B44" t="n">
-        <v>79070</v>
+        <v>58114</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5355,34 +5365,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491825</v>
+        <v>491652</v>
       </c>
       <c r="R44" t="n">
-        <v>6765020</v>
+        <v>6765086</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5425,11 +5440,6 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>I gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,32 +5466,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129148485</v>
+        <v>129146456</v>
       </c>
       <c r="B45" t="n">
-        <v>79070</v>
+        <v>8455</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5491,10 +5501,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491823</v>
+        <v>491626</v>
       </c>
       <c r="R45" t="n">
-        <v>6764963</v>
+        <v>6765093</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5537,11 +5547,6 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter 5 bilder</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5568,50 +5573,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129145705</v>
+        <v>129147916</v>
       </c>
       <c r="B46" t="n">
-        <v>57730</v>
+        <v>97983</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Toktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491605</v>
+        <v>491639</v>
       </c>
       <c r="R46" t="n">
-        <v>6765075</v>
+        <v>6764969</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5654,6 +5654,11 @@
       <c r="AB46" t="inlineStr">
         <is>
           <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Revlummer samt 2 miljöbilder</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 33380-2025 artfynd.xlsx
+++ b/artfynd/A 33380-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129148972</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127840503</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127840604</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127840656</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127840755</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127840997</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1460,6 +1495,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127841273</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1567,6 +1607,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129145482</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1674,6 +1719,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129145950</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1781,6 +1831,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129146949</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1888,6 +1943,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129146972</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1995,6 +2055,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129147059</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2102,6 +2167,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129147148</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2214,6 +2284,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129147300</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2326,6 +2401,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129147358</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2433,6 +2513,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129147379</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2540,6 +2625,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129147406</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2647,6 +2737,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129147438</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2754,6 +2849,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129147806</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2861,6 +2961,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129147986</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2973,6 +3078,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129148294</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3085,6 +3195,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129148408</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3197,6 +3312,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129148485</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3309,6 +3429,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129148524</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3421,6 +3546,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129148571</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3533,6 +3663,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129148629</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3645,6 +3780,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129148685</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3757,6 +3897,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129148866</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3873,6 +4018,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129149060</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3985,6 +4135,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129149092</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4101,6 +4256,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129149409</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4213,6 +4373,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127840817</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4325,6 +4490,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129146427</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4437,6 +4607,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129146529</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4554,6 +4729,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129147170</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4666,6 +4846,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129148592</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4783,6 +4968,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129148839</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4898,6 +5088,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129149167</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5010,6 +5205,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129145705</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5122,6 +5322,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129146351</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5239,6 +5444,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129148942</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5351,6 +5561,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127840593</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5463,6 +5678,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129146961</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5570,6 +5790,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129146456</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5682,8 +5907,60 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129147916</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>